--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>97874</v>
+        <v>98381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mettedet (Mettedet), Jmt</t>
+          <t>Mettedet, Mettedet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -794,10 +794,126 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Thomas Strid, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>117764333</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98381</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mettedet, Mettedet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>556555</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7008446</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tiina Laantee, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98381</v>
+        <v>98389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98381</v>
+        <v>98389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98389</v>
+        <v>98391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98389</v>
+        <v>98391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98391</v>
+        <v>98399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98391</v>
+        <v>98399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Thomas Strid</t>
+          <t>Thomas Strid, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
+          <t>Tiina Laantee, Thomas Strid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98399</v>
+        <v>98402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53947-2023 artfynd.xlsx
+++ b/artfynd/A 53947-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117763554</v>
       </c>
       <c r="B2" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>117764333</v>
       </c>
       <c r="B3" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
